--- a/DAFTAR_DRIVER_TERBARU.xlsx
+++ b/DAFTAR_DRIVER_TERBARU.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="519">
   <si>
     <t>nopol</t>
   </si>
@@ -184,15 +184,9 @@
     <t>B1227HOG</t>
   </si>
   <si>
-    <t>B1827RZG</t>
-  </si>
-  <si>
     <t>F1259AAN</t>
   </si>
   <si>
-    <t>F1843MW</t>
-  </si>
-  <si>
     <t>A1586WB</t>
   </si>
   <si>
@@ -223,9 +217,6 @@
     <t>B2708KRU</t>
   </si>
   <si>
-    <t>F1069ABY</t>
-  </si>
-  <si>
     <t>B1604JKA</t>
   </si>
   <si>
@@ -244,9 +235,6 @@
     <t>F1139FCM</t>
   </si>
   <si>
-    <t>F1532FD</t>
-  </si>
-  <si>
     <t>F1304FAZ</t>
   </si>
   <si>
@@ -268,15 +256,9 @@
     <t>T1243KR</t>
   </si>
   <si>
-    <t>Z1127BB</t>
-  </si>
-  <si>
     <t>B2485SGX</t>
   </si>
   <si>
-    <t>F1830RE</t>
-  </si>
-  <si>
     <t>F1226FCL</t>
   </si>
   <si>
@@ -292,15 +274,6 @@
     <t>F1141FCM</t>
   </si>
   <si>
-    <t>B1116HOG</t>
-  </si>
-  <si>
-    <t>F1348FCC</t>
-  </si>
-  <si>
-    <t>B2596KGT</t>
-  </si>
-  <si>
     <t>F1791AAM</t>
   </si>
   <si>
@@ -316,9 +289,6 @@
     <t>B1374DOP</t>
   </si>
   <si>
-    <t>B1962HFS</t>
-  </si>
-  <si>
     <t>B1068JFP</t>
   </si>
   <si>
@@ -331,24 +301,12 @@
     <t>F1224FCL</t>
   </si>
   <si>
-    <t>B2592KYX</t>
-  </si>
-  <si>
-    <t>B1133EZY</t>
-  </si>
-  <si>
-    <t>F1087FBF</t>
-  </si>
-  <si>
     <t>B1709DOZ</t>
   </si>
   <si>
     <t>F1462FNF</t>
   </si>
   <si>
-    <t>F1208FNF</t>
-  </si>
-  <si>
     <t>B1233EYL</t>
   </si>
   <si>
@@ -367,12 +325,6 @@
     <t>F1730KN</t>
   </si>
   <si>
-    <t>B1950ERH</t>
-  </si>
-  <si>
-    <t>D1050AKD</t>
-  </si>
-  <si>
     <t>B1701EZV</t>
   </si>
   <si>
@@ -385,54 +337,21 @@
     <t>B1275EIG</t>
   </si>
   <si>
-    <t>T1474KR</t>
-  </si>
-  <si>
     <t>F1081ZC</t>
   </si>
   <si>
-    <t>F1226RH</t>
-  </si>
-  <si>
     <t>B1311TZJ</t>
   </si>
   <si>
-    <t>F1637FCA</t>
-  </si>
-  <si>
     <t>F1772NE</t>
   </si>
   <si>
-    <t>D1865AJS</t>
-  </si>
-  <si>
-    <t>T1645HU</t>
-  </si>
-  <si>
     <t>F1582FCD</t>
   </si>
   <si>
-    <t>F1282MS</t>
-  </si>
-  <si>
-    <t>B2573KRC</t>
-  </si>
-  <si>
-    <t>B1288DOJ</t>
-  </si>
-  <si>
-    <t>T1475KQ</t>
-  </si>
-  <si>
-    <t>B1252JKD</t>
-  </si>
-  <si>
     <t>B1385EIF</t>
   </si>
   <si>
-    <t>F1462FCA</t>
-  </si>
-  <si>
     <t>B1592EYP</t>
   </si>
   <si>
@@ -442,156 +361,51 @@
     <t>B2377FOH</t>
   </si>
   <si>
-    <t>F1540PH</t>
-  </si>
-  <si>
     <t>F1433JT</t>
   </si>
   <si>
-    <t>F1014FAZ</t>
-  </si>
-  <si>
-    <t>F1014NC</t>
-  </si>
-  <si>
-    <t>F1492ZC</t>
-  </si>
-  <si>
     <t>B2748FOD</t>
   </si>
   <si>
     <t>F1178FCD</t>
   </si>
   <si>
-    <t>F1353PJ</t>
-  </si>
-  <si>
-    <t>B2018KZS</t>
-  </si>
-  <si>
-    <t>B2046FOB</t>
-  </si>
-  <si>
-    <t>F1629ABT</t>
-  </si>
-  <si>
-    <t>B1961EZP</t>
-  </si>
-  <si>
     <t>D1125AKU</t>
   </si>
   <si>
-    <t>F1494FNC</t>
-  </si>
-  <si>
-    <t>BB1763FE</t>
-  </si>
-  <si>
-    <t>Z1395EM</t>
-  </si>
-  <si>
-    <t>B1147EZL</t>
-  </si>
-  <si>
-    <t>B2695KIT</t>
-  </si>
-  <si>
-    <t>B1658WIY</t>
-  </si>
-  <si>
     <t>E1408JF</t>
   </si>
   <si>
-    <t>F1637VJ</t>
-  </si>
-  <si>
     <t>F1493FBF</t>
   </si>
   <si>
-    <t>B2070KRB</t>
-  </si>
-  <si>
-    <t>F1244FBM</t>
-  </si>
-  <si>
     <t>B1617DOH</t>
   </si>
   <si>
-    <t>B2490FOC</t>
-  </si>
-  <si>
     <t>F1691MR</t>
   </si>
   <si>
     <t>F1140JG</t>
   </si>
   <si>
-    <t>B2327FKA</t>
-  </si>
-  <si>
     <t>F1599YU</t>
   </si>
   <si>
-    <t>B1491UIV</t>
-  </si>
-  <si>
     <t>F1148FAX</t>
   </si>
   <si>
-    <t>B2403TOU</t>
-  </si>
-  <si>
-    <t>B2302FOI</t>
-  </si>
-  <si>
-    <t>F1451ABJ</t>
-  </si>
-  <si>
-    <t>B2793PFP</t>
-  </si>
-  <si>
     <t>B2796FOG</t>
   </si>
   <si>
-    <t>B1779RZG</t>
-  </si>
-  <si>
-    <t>B1054WIY</t>
-  </si>
-  <si>
     <t>F1024JF</t>
   </si>
   <si>
-    <t>B2655UKB</t>
-  </si>
-  <si>
-    <t>B1558NRH</t>
-  </si>
-  <si>
     <t>F1737FBP</t>
   </si>
   <si>
-    <t>F1058ABE</t>
-  </si>
-  <si>
-    <t>B2394PZQ</t>
-  </si>
-  <si>
-    <t>B2580SOL</t>
-  </si>
-  <si>
     <t>F1882FAJ</t>
   </si>
   <si>
-    <t>F1874NS</t>
-  </si>
-  <si>
-    <t>B2797TRQ</t>
-  </si>
-  <si>
-    <t>F1567NO</t>
-  </si>
-  <si>
     <t>SYARIFUDIN NUR MUSZNIR</t>
   </si>
   <si>
@@ -736,15 +550,9 @@
     <t>FERNANDO SEMBIRING</t>
   </si>
   <si>
-    <t>MUHAMMAD DAFFA</t>
-  </si>
-  <si>
     <t>YENDI MULYANDI</t>
   </si>
   <si>
-    <t>ZULHANDIKA GEMA ALBANNI</t>
-  </si>
-  <si>
     <t>FARIANSYAH</t>
   </si>
   <si>
@@ -814,9 +622,6 @@
     <t>LUDHI IRAWAN RAHMADHI</t>
   </si>
   <si>
-    <t>AGUS GUNAWAN</t>
-  </si>
-  <si>
     <t>TOVAN MULYA ABDI</t>
   </si>
   <si>
@@ -835,12 +640,6 @@
     <t>MOH EKSAN</t>
   </si>
   <si>
-    <t>ALHAMD WALSYUKRI</t>
-  </si>
-  <si>
-    <t>AKHMAD ZULKHENDA</t>
-  </si>
-  <si>
     <t>STEPHANUS ANDREAS SASTIADI ACHTI</t>
   </si>
   <si>
@@ -865,9 +664,6 @@
     <t>RONNY SUWITNA</t>
   </si>
   <si>
-    <t>INDRA SURYANA</t>
-  </si>
-  <si>
     <t>MOH.DALER</t>
   </si>
   <si>
@@ -892,9 +688,6 @@
     <t>FAJAR ADHA</t>
   </si>
   <si>
-    <t>RIZKY SUBARKAH</t>
-  </si>
-  <si>
     <t>RIO APRIMA</t>
   </si>
   <si>
@@ -907,42 +700,18 @@
     <t>RIYO SUPANCA</t>
   </si>
   <si>
-    <t>SUHERMAN</t>
-  </si>
-  <si>
     <t>HARI SAMPURNA DJAYA</t>
   </si>
   <si>
-    <t>DAHLAN JAELANI</t>
-  </si>
-  <si>
     <t>SEWA REGULER</t>
   </si>
   <si>
     <t>TARMUZI</t>
   </si>
   <si>
-    <t>SANDY BERTO NATALY POJOH</t>
-  </si>
-  <si>
-    <t>TATANG JERI PRITYATNA</t>
-  </si>
-  <si>
     <t>PURNOMO</t>
   </si>
   <si>
-    <t>MOHAMAD MUHTAR</t>
-  </si>
-  <si>
-    <t>M FIKRI MAULANA</t>
-  </si>
-  <si>
-    <t>SAFRIAL</t>
-  </si>
-  <si>
-    <t>AHMAD SYARIF SETIADI</t>
-  </si>
-  <si>
     <t>ACHMAD CHAERUDIN</t>
   </si>
   <si>
@@ -955,129 +724,51 @@
     <t>ADE KUSYANA</t>
   </si>
   <si>
-    <t>CATUR AGUNG DEWA SHAKTI</t>
-  </si>
-  <si>
     <t>RIZKY EKA SAPUTRA</t>
   </si>
   <si>
-    <t>YUSUF</t>
-  </si>
-  <si>
-    <t>ARWAN DARWIS</t>
-  </si>
-  <si>
-    <t>SUGIHARTANA</t>
-  </si>
-  <si>
     <t>HADI FAHMIDI</t>
   </si>
   <si>
     <t>RUDY SETIAWAN</t>
   </si>
   <si>
-    <t>SIGIT PRIAMBONO</t>
-  </si>
-  <si>
-    <t>ASEP SAEPUDIN</t>
-  </si>
-  <si>
-    <t>AMID ABDUL RAHIM</t>
-  </si>
-  <si>
     <t>EDO HERMAWAN</t>
   </si>
   <si>
-    <t>STANLY OSCAR</t>
-  </si>
-  <si>
-    <t>MUHAMMAD FAHRIZAL</t>
-  </si>
-  <si>
-    <t>EDISON Y TINAMBUNAN</t>
-  </si>
-  <si>
-    <t>BUDIMERIANTO</t>
-  </si>
-  <si>
     <t>AANG ANDRE PRATAMA</t>
   </si>
   <si>
-    <t>KHEMER TAMBUNAN</t>
-  </si>
-  <si>
     <t>TAUFIQ MAULANA</t>
   </si>
   <si>
-    <t>ERWIN ANOM</t>
-  </si>
-  <si>
-    <t>FAHRIAN ZAYADI AHMAD</t>
-  </si>
-  <si>
     <t>RUDIYANSAH</t>
   </si>
   <si>
-    <t>HIDAYATULLAH</t>
-  </si>
-  <si>
     <t>THET KIONG</t>
   </si>
   <si>
     <t>DANIEL ARIF PANTORO</t>
   </si>
   <si>
-    <t>NURUL MUSTOPA</t>
-  </si>
-  <si>
     <t>IRWAN SEPTIANSYAH</t>
   </si>
   <si>
     <t>SYAIFULLAH</t>
   </si>
   <si>
-    <t>HERI PRIATNA</t>
-  </si>
-  <si>
-    <t>ANDRI SUHADA</t>
-  </si>
-  <si>
     <t>DJAKA LAIDI</t>
   </si>
   <si>
-    <t>AIRLANGGA PATRIA NUSA</t>
-  </si>
-  <si>
-    <t>MUHAMAD AZHAR RINALDI</t>
-  </si>
-  <si>
     <t>MUHAMAD FAIZ PRADIPTA</t>
   </si>
   <si>
-    <t>NOVRI ANGGRIAWAN</t>
-  </si>
-  <si>
     <t>EKO SUPRIYANTO</t>
   </si>
   <si>
-    <t>HARI MUSLIHAT</t>
-  </si>
-  <si>
-    <t>RAHMADONI</t>
-  </si>
-  <si>
     <t>SLAMET SANTOSO</t>
   </si>
   <si>
-    <t>FAJAR SIDIK</t>
-  </si>
-  <si>
-    <t>AJI TRIMULYA</t>
-  </si>
-  <si>
-    <t>TERRY DEKS METHALELA</t>
-  </si>
-  <si>
     <t>083825197414</t>
   </si>
   <si>
@@ -1222,15 +913,9 @@
     <t>081219586007</t>
   </si>
   <si>
-    <t>81316387307</t>
-  </si>
-  <si>
     <t>081228743473</t>
   </si>
   <si>
-    <t>+6283876395166</t>
-  </si>
-  <si>
     <t>085117448114</t>
   </si>
   <si>
@@ -1300,9 +985,6 @@
     <t>085348455848</t>
   </si>
   <si>
-    <t>085220266841</t>
-  </si>
-  <si>
     <t>081283803171</t>
   </si>
   <si>
@@ -1321,12 +1003,6 @@
     <t>081398048832</t>
   </si>
   <si>
-    <t>081291689765</t>
-  </si>
-  <si>
-    <t>081290864974</t>
-  </si>
-  <si>
     <t>081382228979</t>
   </si>
   <si>
@@ -1351,9 +1027,6 @@
     <t>081228987173</t>
   </si>
   <si>
-    <t>082126810557</t>
-  </si>
-  <si>
     <t>081292268897</t>
   </si>
   <si>
@@ -1378,9 +1051,6 @@
     <t>082298371267</t>
   </si>
   <si>
-    <t>0895321720502</t>
-  </si>
-  <si>
     <t>0895402967350</t>
   </si>
   <si>
@@ -1393,42 +1063,18 @@
     <t>082122445205</t>
   </si>
   <si>
-    <t>082315952167</t>
-  </si>
-  <si>
     <t>082117238245</t>
   </si>
   <si>
-    <t>085692783980</t>
-  </si>
-  <si>
     <t>08123456789</t>
   </si>
   <si>
     <t>081281575976</t>
   </si>
   <si>
-    <t>081213297168</t>
-  </si>
-  <si>
-    <t>085714582296</t>
-  </si>
-  <si>
     <t>085922453197</t>
   </si>
   <si>
-    <t>081310294297</t>
-  </si>
-  <si>
-    <t>085888818832</t>
-  </si>
-  <si>
-    <t>081316891836</t>
-  </si>
-  <si>
-    <t>087834013288</t>
-  </si>
-  <si>
     <t>085894659130</t>
   </si>
   <si>
@@ -1441,129 +1087,51 @@
     <t>081226813381</t>
   </si>
   <si>
-    <t>085866117257</t>
-  </si>
-  <si>
     <t>085882378646</t>
   </si>
   <si>
-    <t>085710553822</t>
-  </si>
-  <si>
-    <t>081298044556</t>
-  </si>
-  <si>
-    <t>081371912623</t>
-  </si>
-  <si>
     <t>082124460616</t>
   </si>
   <si>
     <t>082334579095</t>
   </si>
   <si>
-    <t>081286503065</t>
-  </si>
-  <si>
-    <t>085810345268</t>
-  </si>
-  <si>
-    <t>88976686957</t>
-  </si>
-  <si>
     <t>087847166750</t>
   </si>
   <si>
-    <t>081210935595</t>
-  </si>
-  <si>
-    <t>081291577774</t>
-  </si>
-  <si>
-    <t>082112465098</t>
-  </si>
-  <si>
-    <t>085811165314</t>
-  </si>
-  <si>
     <t>081316976920</t>
   </si>
   <si>
-    <t>081386953548</t>
-  </si>
-  <si>
     <t>082311323197</t>
   </si>
   <si>
-    <t>088905741696</t>
-  </si>
-  <si>
-    <t>087759262587</t>
-  </si>
-  <si>
     <t>08568010624</t>
   </si>
   <si>
-    <t>085282937994</t>
-  </si>
-  <si>
     <t>081290288899</t>
   </si>
   <si>
     <t>08111764650</t>
   </si>
   <si>
-    <t>085776568708</t>
-  </si>
-  <si>
     <t>081212849026</t>
   </si>
   <si>
     <t>081318925530</t>
   </si>
   <si>
-    <t>081297094515</t>
-  </si>
-  <si>
-    <t>081292743939</t>
-  </si>
-  <si>
     <t>085881634276</t>
   </si>
   <si>
-    <t>083136155160</t>
-  </si>
-  <si>
-    <t>089515551043</t>
-  </si>
-  <si>
     <t>085779479007</t>
   </si>
   <si>
-    <t>08990322561</t>
-  </si>
-  <si>
     <t>082112395345</t>
   </si>
   <si>
-    <t>085779195590</t>
-  </si>
-  <si>
-    <t>083173148265</t>
-  </si>
-  <si>
     <t>087711144892</t>
   </si>
   <si>
-    <t>081295144101</t>
-  </si>
-  <si>
-    <t>081292441068</t>
-  </si>
-  <si>
-    <t>081281722882</t>
-  </si>
-  <si>
     <t>Daihatsu</t>
   </si>
   <si>
@@ -1582,9 +1150,6 @@
     <t>Nissan</t>
   </si>
   <si>
-    <t>Wuling</t>
-  </si>
-  <si>
     <t>Honda</t>
   </si>
   <si>
@@ -1627,33 +1192,9 @@
     <t>VFe34</t>
   </si>
   <si>
-    <t>CONFERO</t>
-  </si>
-  <si>
     <t>Brio Satya</t>
   </si>
   <si>
-    <t>TERIOS</t>
-  </si>
-  <si>
-    <t>ALL NEW AVANZA</t>
-  </si>
-  <si>
-    <t>BRIO</t>
-  </si>
-  <si>
-    <t>AGYA</t>
-  </si>
-  <si>
-    <t>VELOZ</t>
-  </si>
-  <si>
-    <t>Brio RS</t>
-  </si>
-  <si>
-    <t>MOBILIO</t>
-  </si>
-  <si>
     <t>Kosong</t>
   </si>
   <si>
@@ -1810,15 +1351,9 @@
     <t>2026-06-08 08:59:45</t>
   </si>
   <si>
-    <t>2026-06-07 21:30:27</t>
-  </si>
-  <si>
     <t>2026-06-05 09:50:12</t>
   </si>
   <si>
-    <t>2026-05-29 17:37:07</t>
-  </si>
-  <si>
     <t>2026-05-29 15:03:47</t>
   </si>
   <si>
@@ -1849,9 +1384,6 @@
     <t>2026-05-17 14:49:07</t>
   </si>
   <si>
-    <t>2026-05-15 17:32:13</t>
-  </si>
-  <si>
     <t>2026-05-12 16:48:09</t>
   </si>
   <si>
@@ -1870,9 +1402,6 @@
     <t>2026-04-30 19:13:25</t>
   </si>
   <si>
-    <t>2026-04-28 10:19:59</t>
-  </si>
-  <si>
     <t>2026-04-27 16:25:43</t>
   </si>
   <si>
@@ -1894,15 +1423,9 @@
     <t>2026-03-28 18:02:24</t>
   </si>
   <si>
-    <t>2026-03-26 10:15:27</t>
-  </si>
-  <si>
     <t>2026-03-23 09:33:07</t>
   </si>
   <si>
-    <t>2026-03-11 11:12:23</t>
-  </si>
-  <si>
     <t>2026-03-11 10:57:19</t>
   </si>
   <si>
@@ -1918,15 +1441,6 @@
     <t>2026-03-04 20:05:48</t>
   </si>
   <si>
-    <t>2026-03-04 19:41:49</t>
-  </si>
-  <si>
-    <t>2026-03-03 16:25:00</t>
-  </si>
-  <si>
-    <t>2026-03-03 14:25:25</t>
-  </si>
-  <si>
     <t>2026-02-21 18:39:25</t>
   </si>
   <si>
@@ -1942,9 +1456,6 @@
     <t>2026-02-14 14:02:03</t>
   </si>
   <si>
-    <t>2026-02-10 12:39:55</t>
-  </si>
-  <si>
     <t>2026-02-07 11:44:41</t>
   </si>
   <si>
@@ -1957,24 +1468,12 @@
     <t>2026-02-03 20:01:18</t>
   </si>
   <si>
-    <t>2026-02-03 10:08:50</t>
-  </si>
-  <si>
-    <t>2026-01-29 12:16:07</t>
-  </si>
-  <si>
-    <t>2026-01-29 10:10:18</t>
-  </si>
-  <si>
     <t>2026-01-27 11:12:45</t>
   </si>
   <si>
     <t>2026-01-26 10:00:22</t>
   </si>
   <si>
-    <t>2026-01-21 11:03:46</t>
-  </si>
-  <si>
     <t>2026-01-09 19:42:24</t>
   </si>
   <si>
@@ -1993,12 +1492,6 @@
     <t>2025-11-27 12:11:58</t>
   </si>
   <si>
-    <t>2025-11-27 10:25:13</t>
-  </si>
-  <si>
-    <t>2025-11-21 18:36:31</t>
-  </si>
-  <si>
     <t>2025-11-19 16:47:23</t>
   </si>
   <si>
@@ -2011,54 +1504,21 @@
     <t>2025-11-13 14:47:25</t>
   </si>
   <si>
-    <t>2025-11-10 18:57:16</t>
-  </si>
-  <si>
     <t>2025-11-08 18:31:20</t>
   </si>
   <si>
-    <t>2025-11-08 11:30:30</t>
-  </si>
-  <si>
     <t>2025-11-07 06:15:57</t>
   </si>
   <si>
-    <t>2025-10-13 18:04:34</t>
-  </si>
-  <si>
     <t>2025-10-08 09:42:57</t>
   </si>
   <si>
-    <t>2025-10-02 18:09:10</t>
-  </si>
-  <si>
-    <t>2025-09-26 09:38:34</t>
-  </si>
-  <si>
     <t>2025-09-24 09:27:03</t>
   </si>
   <si>
-    <t>2025-09-18 20:18:16</t>
-  </si>
-  <si>
-    <t>2025-09-13 15:54:06</t>
-  </si>
-  <si>
-    <t>2025-09-13 10:02:49</t>
-  </si>
-  <si>
-    <t>2025-09-12 22:54:53</t>
-  </si>
-  <si>
-    <t>2025-09-11 10:38:09</t>
-  </si>
-  <si>
     <t>2025-09-11 09:42:20</t>
   </si>
   <si>
-    <t>2025-09-04 09:10:55</t>
-  </si>
-  <si>
     <t>2025-09-03 22:00:27</t>
   </si>
   <si>
@@ -2068,154 +1528,49 @@
     <t>2025-09-01 12:16:27</t>
   </si>
   <si>
-    <t>2025-08-28 20:51:13</t>
-  </si>
-  <si>
     <t>2025-08-21 11:31:29</t>
   </si>
   <si>
-    <t>2025-08-14 11:56:52</t>
-  </si>
-  <si>
-    <t>2025-08-13 19:19:31</t>
-  </si>
-  <si>
-    <t>2025-08-12 17:33:31</t>
-  </si>
-  <si>
     <t>2025-07-11 11:08:34</t>
   </si>
   <si>
     <t>2025-07-07 09:29:56</t>
   </si>
   <si>
-    <t>2025-07-04 13:50:31</t>
-  </si>
-  <si>
-    <t>2025-06-26 18:50:37</t>
-  </si>
-  <si>
-    <t>2025-06-17 12:51:03</t>
-  </si>
-  <si>
-    <t>2025-06-07 16:50:43</t>
-  </si>
-  <si>
-    <t>2025-06-03 18:10:03</t>
-  </si>
-  <si>
     <t>2025-06-03 09:21:29</t>
   </si>
   <si>
-    <t>2025-05-28 16:28:13</t>
-  </si>
-  <si>
-    <t>2025-05-28 11:32:01</t>
-  </si>
-  <si>
-    <t>2025-05-27 08:28:21</t>
-  </si>
-  <si>
-    <t>2025-05-26 13:17:40</t>
-  </si>
-  <si>
-    <t>2025-05-02 17:46:11</t>
-  </si>
-  <si>
-    <t>2025-04-30 19:02:09</t>
-  </si>
-  <si>
     <t>2025-04-22 09:43:05</t>
   </si>
   <si>
-    <t>2025-04-16 19:13:48</t>
-  </si>
-  <si>
     <t>2025-04-02 10:44:46</t>
   </si>
   <si>
-    <t>2025-03-19 16:05:07</t>
-  </si>
-  <si>
-    <t>2025-03-07 11:09:36</t>
-  </si>
-  <si>
     <t>2025-02-25 11:17:20</t>
   </si>
   <si>
-    <t>2025-02-17 11:54:07</t>
-  </si>
-  <si>
     <t>2025-02-12 13:37:36</t>
   </si>
   <si>
     <t>2025-01-24 10:38:50</t>
   </si>
   <si>
-    <t>2024-12-30 22:12:59</t>
-  </si>
-  <si>
     <t>2024-12-28 15:02:18</t>
   </si>
   <si>
-    <t>2024-12-17 17:29:46</t>
-  </si>
-  <si>
     <t>2024-11-04 15:44:02</t>
   </si>
   <si>
-    <t>2024-09-28 20:52:03</t>
-  </si>
-  <si>
-    <t>2024-09-25 09:52:12</t>
-  </si>
-  <si>
-    <t>2024-09-21 23:27:56</t>
-  </si>
-  <si>
-    <t>2024-09-18 10:29:47</t>
-  </si>
-  <si>
     <t>2024-09-15 23:53:42</t>
   </si>
   <si>
-    <t>2024-09-05 22:54:08</t>
-  </si>
-  <si>
-    <t>2024-09-05 22:51:38</t>
-  </si>
-  <si>
     <t>2024-09-04 22:56:03</t>
   </si>
   <si>
-    <t>2024-07-11 18:16:45</t>
-  </si>
-  <si>
-    <t>2024-06-05 13:10:03</t>
-  </si>
-  <si>
     <t>2024-05-25 19:44:19</t>
   </si>
   <si>
-    <t>2024-05-11 23:01:11</t>
-  </si>
-  <si>
-    <t>2024-04-22 00:29:44</t>
-  </si>
-  <si>
-    <t>2023-10-06 08:32:54</t>
-  </si>
-  <si>
     <t>2023-06-05 13:50:30</t>
-  </si>
-  <si>
-    <t>2023-05-23 23:43:29</t>
-  </si>
-  <si>
-    <t>2023-05-08 10:07:16</t>
-  </si>
-  <si>
-    <t>2023-03-11 09:07:45</t>
   </si>
 </sst>
 </file>
@@ -2547,7 +1902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2578,22 +1933,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>354</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F2" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G2" t="s">
-        <v>549</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2601,22 +1956,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>193</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>355</v>
+        <v>252</v>
       </c>
       <c r="D3" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E3" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F3" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G3" t="s">
-        <v>550</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2624,22 +1979,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>356</v>
+        <v>253</v>
       </c>
       <c r="D4" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E4" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F4" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G4" t="s">
-        <v>551</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2647,22 +2002,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
-        <v>354</v>
+        <v>251</v>
       </c>
       <c r="D5" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E5" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F5" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G5" t="s">
-        <v>552</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2670,22 +2025,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>357</v>
+        <v>254</v>
       </c>
       <c r="D6" t="s">
-        <v>517</v>
+        <v>373</v>
       </c>
       <c r="E6" t="s">
-        <v>525</v>
+        <v>380</v>
       </c>
       <c r="F6" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G6" t="s">
-        <v>553</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2693,22 +2048,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>358</v>
+        <v>255</v>
       </c>
       <c r="D7" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E7" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F7" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G7" t="s">
-        <v>554</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2716,22 +2071,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>359</v>
+        <v>256</v>
       </c>
       <c r="D8" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E8" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F8" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G8" t="s">
-        <v>555</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2739,22 +2094,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="D9" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E9" t="s">
-        <v>526</v>
+        <v>381</v>
       </c>
       <c r="F9" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G9" t="s">
-        <v>556</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2762,22 +2117,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>361</v>
+        <v>258</v>
       </c>
       <c r="D10" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E10" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F10" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G10" t="s">
-        <v>557</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2785,22 +2140,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>362</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E11" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F11" t="s">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="G11" t="s">
-        <v>558</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2808,22 +2163,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>363</v>
+        <v>260</v>
       </c>
       <c r="D12" t="s">
-        <v>518</v>
+        <v>374</v>
       </c>
       <c r="E12" t="s">
-        <v>527</v>
+        <v>382</v>
       </c>
       <c r="F12" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G12" t="s">
-        <v>559</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2831,22 +2186,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>140</v>
       </c>
       <c r="C13" t="s">
-        <v>364</v>
+        <v>261</v>
       </c>
       <c r="D13" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E13" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F13" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G13" t="s">
-        <v>560</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2854,22 +2209,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>365</v>
+        <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E14" t="s">
-        <v>528</v>
+        <v>383</v>
       </c>
       <c r="F14" t="s">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="G14" t="s">
-        <v>561</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2877,22 +2232,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="C15" t="s">
-        <v>366</v>
+        <v>263</v>
       </c>
       <c r="D15" t="s">
-        <v>520</v>
+        <v>376</v>
       </c>
       <c r="E15" t="s">
-        <v>529</v>
+        <v>384</v>
       </c>
       <c r="F15" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G15" t="s">
-        <v>562</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2900,22 +2255,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="C16" t="s">
-        <v>367</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>520</v>
+        <v>376</v>
       </c>
       <c r="E16" t="s">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="F16" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G16" t="s">
-        <v>563</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2923,22 +2278,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="C17" t="s">
-        <v>368</v>
+        <v>265</v>
       </c>
       <c r="D17" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E17" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F17" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G17" t="s">
-        <v>564</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2946,22 +2301,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="C18" t="s">
-        <v>369</v>
+        <v>266</v>
       </c>
       <c r="D18" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E18" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F18" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G18" t="s">
-        <v>565</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2969,22 +2324,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>370</v>
+        <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E19" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F19" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G19" t="s">
-        <v>566</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2992,22 +2347,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
-        <v>371</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E20" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F20" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G20" t="s">
-        <v>567</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3015,22 +2370,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="C21" t="s">
-        <v>372</v>
+        <v>269</v>
       </c>
       <c r="D21" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E21" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F21" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G21" t="s">
-        <v>568</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3038,22 +2393,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
       <c r="C22" t="s">
-        <v>373</v>
+        <v>270</v>
       </c>
       <c r="D22" t="s">
-        <v>520</v>
+        <v>376</v>
       </c>
       <c r="E22" t="s">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="F22" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G22" t="s">
-        <v>569</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3061,22 +2416,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>212</v>
+        <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>374</v>
+        <v>271</v>
       </c>
       <c r="D23" t="s">
-        <v>521</v>
+        <v>377</v>
       </c>
       <c r="E23" t="s">
-        <v>531</v>
+        <v>386</v>
       </c>
       <c r="F23" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G23" t="s">
-        <v>570</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3084,22 +2439,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>151</v>
       </c>
       <c r="C24" t="s">
-        <v>375</v>
+        <v>272</v>
       </c>
       <c r="D24" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E24" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F24" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G24" t="s">
-        <v>571</v>
+        <v>418</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3107,22 +2462,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>376</v>
+        <v>273</v>
       </c>
       <c r="D25" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E25" t="s">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="F25" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G25" t="s">
-        <v>572</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3130,22 +2485,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>215</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
-        <v>377</v>
+        <v>274</v>
       </c>
       <c r="D26" t="s">
-        <v>520</v>
+        <v>376</v>
       </c>
       <c r="E26" t="s">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="F26" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G26" t="s">
-        <v>573</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3153,22 +2508,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>216</v>
+        <v>154</v>
       </c>
       <c r="C27" t="s">
-        <v>378</v>
+        <v>275</v>
       </c>
       <c r="D27" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E27" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F27" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G27" t="s">
-        <v>574</v>
+        <v>421</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3176,22 +2531,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
-        <v>379</v>
+        <v>276</v>
       </c>
       <c r="D28" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E28" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F28" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G28" t="s">
-        <v>575</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3199,22 +2554,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="C29" t="s">
-        <v>380</v>
+        <v>277</v>
       </c>
       <c r="D29" t="s">
-        <v>520</v>
+        <v>376</v>
       </c>
       <c r="E29" t="s">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="F29" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G29" t="s">
-        <v>576</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3222,22 +2577,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="C30" t="s">
-        <v>381</v>
+        <v>278</v>
       </c>
       <c r="D30" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E30" t="s">
-        <v>533</v>
+        <v>388</v>
       </c>
       <c r="F30" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G30" t="s">
-        <v>577</v>
+        <v>424</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3245,22 +2600,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="C31" t="s">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="D31" t="s">
-        <v>520</v>
+        <v>376</v>
       </c>
       <c r="E31" t="s">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="F31" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G31" t="s">
-        <v>578</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3268,22 +2623,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="C32" t="s">
-        <v>383</v>
+        <v>280</v>
       </c>
       <c r="D32" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E32" t="s">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="F32" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G32" t="s">
-        <v>579</v>
+        <v>426</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3291,22 +2646,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="C33" t="s">
-        <v>384</v>
+        <v>281</v>
       </c>
       <c r="D33" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E33" t="s">
-        <v>534</v>
+        <v>389</v>
       </c>
       <c r="F33" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G33" t="s">
-        <v>580</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3314,22 +2669,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="C34" t="s">
-        <v>385</v>
+        <v>282</v>
       </c>
       <c r="D34" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E34" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F34" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G34" t="s">
-        <v>581</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3337,22 +2692,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>224</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
-        <v>386</v>
+        <v>283</v>
       </c>
       <c r="D35" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E35" t="s">
-        <v>528</v>
+        <v>383</v>
       </c>
       <c r="F35" t="s">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="G35" t="s">
-        <v>582</v>
+        <v>429</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3360,22 +2715,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>163</v>
       </c>
       <c r="C36" t="s">
-        <v>387</v>
+        <v>284</v>
       </c>
       <c r="D36" t="s">
-        <v>520</v>
+        <v>376</v>
       </c>
       <c r="E36" t="s">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="F36" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G36" t="s">
-        <v>583</v>
+        <v>430</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -3383,22 +2738,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="C37" t="s">
-        <v>388</v>
+        <v>285</v>
       </c>
       <c r="D37" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E37" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F37" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G37" t="s">
-        <v>584</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3406,22 +2761,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
+        <v>165</v>
       </c>
       <c r="C38" t="s">
-        <v>389</v>
+        <v>286</v>
       </c>
       <c r="D38" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E38" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F38" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G38" t="s">
-        <v>585</v>
+        <v>432</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3429,22 +2784,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="C39" t="s">
+        <v>287</v>
+      </c>
+      <c r="D39" t="s">
+        <v>372</v>
+      </c>
+      <c r="E39" t="s">
         <v>390</v>
       </c>
-      <c r="D39" t="s">
-        <v>516</v>
-      </c>
-      <c r="E39" t="s">
-        <v>535</v>
-      </c>
       <c r="F39" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G39" t="s">
-        <v>586</v>
+        <v>433</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3452,22 +2807,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="C40" t="s">
-        <v>391</v>
+        <v>288</v>
       </c>
       <c r="D40" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E40" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F40" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G40" t="s">
-        <v>587</v>
+        <v>434</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -3475,22 +2830,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
       <c r="C41" t="s">
-        <v>392</v>
+        <v>289</v>
       </c>
       <c r="D41" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E41" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F41" t="s">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="G41" t="s">
-        <v>588</v>
+        <v>435</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3498,22 +2853,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>231</v>
+        <v>169</v>
       </c>
       <c r="C42" t="s">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="D42" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E42" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F42" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G42" t="s">
-        <v>589</v>
+        <v>436</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3521,22 +2876,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="C43" t="s">
-        <v>394</v>
+        <v>291</v>
       </c>
       <c r="D43" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E43" t="s">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="F43" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G43" t="s">
-        <v>590</v>
+        <v>437</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3544,22 +2899,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>233</v>
+        <v>171</v>
       </c>
       <c r="C44" t="s">
+        <v>292</v>
+      </c>
+      <c r="D44" t="s">
+        <v>372</v>
+      </c>
+      <c r="E44" t="s">
+        <v>379</v>
+      </c>
+      <c r="F44" t="s">
         <v>395</v>
       </c>
-      <c r="D44" t="s">
-        <v>516</v>
-      </c>
-      <c r="E44" t="s">
-        <v>524</v>
-      </c>
-      <c r="F44" t="s">
-        <v>548</v>
-      </c>
       <c r="G44" t="s">
-        <v>591</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3567,22 +2922,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>234</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>396</v>
+        <v>293</v>
       </c>
       <c r="D45" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E45" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F45" t="s">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="G45" t="s">
-        <v>592</v>
+        <v>439</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3590,22 +2945,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>235</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
-        <v>397</v>
+        <v>294</v>
       </c>
       <c r="D46" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E46" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F46" t="s">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="G46" t="s">
-        <v>593</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3613,22 +2968,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>236</v>
+        <v>174</v>
       </c>
       <c r="C47" t="s">
-        <v>398</v>
+        <v>295</v>
       </c>
       <c r="D47" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E47" t="s">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="F47" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G47" t="s">
-        <v>594</v>
+        <v>441</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3636,22 +2991,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>237</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s">
-        <v>399</v>
+        <v>296</v>
       </c>
       <c r="D48" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E48" t="s">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="F48" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G48" t="s">
-        <v>595</v>
+        <v>442</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3659,22 +3014,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>238</v>
+        <v>176</v>
       </c>
       <c r="C49" t="s">
-        <v>400</v>
+        <v>297</v>
       </c>
       <c r="D49" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E49" t="s">
-        <v>526</v>
+        <v>381</v>
       </c>
       <c r="F49" t="s">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="G49" t="s">
-        <v>596</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3682,22 +3037,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>239</v>
+        <v>177</v>
       </c>
       <c r="C50" t="s">
-        <v>401</v>
+        <v>298</v>
       </c>
       <c r="D50" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E50" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F50" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G50" t="s">
-        <v>597</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3705,22 +3060,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="C51" t="s">
-        <v>402</v>
+        <v>299</v>
       </c>
       <c r="D51" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E51" t="s">
-        <v>528</v>
+        <v>383</v>
       </c>
       <c r="F51" t="s">
-        <v>548</v>
+        <v>393</v>
       </c>
       <c r="G51" t="s">
-        <v>598</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3728,22 +3083,22 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>241</v>
+        <v>179</v>
       </c>
       <c r="C52" t="s">
-        <v>403</v>
+        <v>300</v>
       </c>
       <c r="D52" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E52" t="s">
-        <v>528</v>
+        <v>379</v>
       </c>
       <c r="F52" t="s">
-        <v>546</v>
+        <v>394</v>
       </c>
       <c r="G52" t="s">
-        <v>599</v>
+        <v>446</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3751,22 +3106,22 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>242</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
-        <v>404</v>
+        <v>301</v>
       </c>
       <c r="D53" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E53" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F53" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G53" t="s">
-        <v>600</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3774,22 +3129,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>243</v>
+        <v>181</v>
       </c>
       <c r="C54" t="s">
-        <v>405</v>
+        <v>302</v>
       </c>
       <c r="D54" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E54" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F54" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G54" t="s">
-        <v>601</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3797,22 +3152,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
       <c r="C55" t="s">
-        <v>406</v>
+        <v>303</v>
       </c>
       <c r="D55" t="s">
-        <v>516</v>
+        <v>376</v>
       </c>
       <c r="E55" t="s">
-        <v>524</v>
+        <v>385</v>
       </c>
       <c r="F55" t="s">
-        <v>547</v>
+        <v>393</v>
       </c>
       <c r="G55" t="s">
-        <v>602</v>
+        <v>449</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3820,22 +3175,22 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>245</v>
+        <v>183</v>
       </c>
       <c r="C56" t="s">
-        <v>407</v>
+        <v>304</v>
       </c>
       <c r="D56" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E56" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F56" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G56" t="s">
-        <v>603</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3843,22 +3198,22 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>246</v>
+        <v>184</v>
       </c>
       <c r="C57" t="s">
-        <v>408</v>
+        <v>305</v>
       </c>
       <c r="D57" t="s">
-        <v>520</v>
+        <v>376</v>
       </c>
       <c r="E57" t="s">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="F57" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G57" t="s">
-        <v>604</v>
+        <v>451</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3866,22 +3221,22 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>247</v>
+        <v>185</v>
       </c>
       <c r="C58" t="s">
-        <v>409</v>
+        <v>306</v>
       </c>
       <c r="D58" t="s">
-        <v>516</v>
+        <v>376</v>
       </c>
       <c r="E58" t="s">
-        <v>524</v>
+        <v>385</v>
       </c>
       <c r="F58" t="s">
-        <v>547</v>
+        <v>393</v>
       </c>
       <c r="G58" t="s">
-        <v>605</v>
+        <v>452</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3889,22 +3244,22 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>248</v>
+        <v>186</v>
       </c>
       <c r="C59" t="s">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="D59" t="s">
-        <v>520</v>
+        <v>375</v>
       </c>
       <c r="E59" t="s">
-        <v>530</v>
+        <v>387</v>
       </c>
       <c r="F59" t="s">
-        <v>546</v>
+        <v>394</v>
       </c>
       <c r="G59" t="s">
-        <v>606</v>
+        <v>453</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3912,22 +3267,22 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>249</v>
+        <v>187</v>
       </c>
       <c r="C60" t="s">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="D60" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E60" t="s">
-        <v>530</v>
+        <v>379</v>
       </c>
       <c r="F60" t="s">
-        <v>546</v>
+        <v>395</v>
       </c>
       <c r="G60" t="s">
-        <v>607</v>
+        <v>454</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3935,22 +3290,22 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="C61" t="s">
-        <v>412</v>
+        <v>309</v>
       </c>
       <c r="D61" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E61" t="s">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="F61" t="s">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="G61" t="s">
-        <v>608</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3958,22 +3313,22 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>251</v>
+        <v>189</v>
       </c>
       <c r="C62" t="s">
-        <v>413</v>
+        <v>310</v>
       </c>
       <c r="D62" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E62" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F62" t="s">
-        <v>548</v>
+        <v>393</v>
       </c>
       <c r="G62" t="s">
-        <v>609</v>
+        <v>456</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3981,22 +3336,22 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>252</v>
+        <v>190</v>
       </c>
       <c r="C63" t="s">
-        <v>414</v>
+        <v>311</v>
       </c>
       <c r="D63" t="s">
-        <v>519</v>
+        <v>376</v>
       </c>
       <c r="E63" t="s">
-        <v>532</v>
+        <v>384</v>
       </c>
       <c r="F63" t="s">
-        <v>548</v>
+        <v>393</v>
       </c>
       <c r="G63" t="s">
-        <v>610</v>
+        <v>457</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -4004,22 +3359,22 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="C64" t="s">
-        <v>371</v>
+        <v>312</v>
       </c>
       <c r="D64" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E64" t="s">
-        <v>524</v>
+        <v>387</v>
       </c>
       <c r="F64" t="s">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="G64" t="s">
-        <v>611</v>
+        <v>458</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -4027,22 +3382,22 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>415</v>
+        <v>313</v>
       </c>
       <c r="D65" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E65" t="s">
-        <v>524</v>
+        <v>387</v>
       </c>
       <c r="F65" t="s">
-        <v>546</v>
+        <v>394</v>
       </c>
       <c r="G65" t="s">
-        <v>612</v>
+        <v>459</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -4050,22 +3405,22 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="C66" t="s">
-        <v>416</v>
+        <v>314</v>
       </c>
       <c r="D66" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E66" t="s">
-        <v>529</v>
+        <v>379</v>
       </c>
       <c r="F66" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="G66" t="s">
-        <v>613</v>
+        <v>460</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -4073,22 +3428,22 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="C67" t="s">
-        <v>417</v>
+        <v>315</v>
       </c>
       <c r="D67" t="s">
-        <v>519</v>
+        <v>376</v>
       </c>
       <c r="E67" t="s">
-        <v>532</v>
+        <v>385</v>
       </c>
       <c r="F67" t="s">
-        <v>548</v>
+        <v>393</v>
       </c>
       <c r="G67" t="s">
-        <v>614</v>
+        <v>461</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -4096,22 +3451,22 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="C68" t="s">
-        <v>418</v>
+        <v>316</v>
       </c>
       <c r="D68" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E68" t="s">
-        <v>532</v>
+        <v>379</v>
       </c>
       <c r="F68" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G68" t="s">
-        <v>615</v>
+        <v>462</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4119,22 +3474,22 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="C69" t="s">
-        <v>419</v>
+        <v>317</v>
       </c>
       <c r="D69" t="s">
-        <v>516</v>
+        <v>376</v>
       </c>
       <c r="E69" t="s">
-        <v>524</v>
+        <v>391</v>
       </c>
       <c r="F69" t="s">
-        <v>546</v>
+        <v>394</v>
       </c>
       <c r="G69" t="s">
-        <v>616</v>
+        <v>463</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4142,22 +3497,22 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="C70" t="s">
-        <v>420</v>
+        <v>318</v>
       </c>
       <c r="D70" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E70" t="s">
-        <v>530</v>
+        <v>379</v>
       </c>
       <c r="F70" t="s">
-        <v>546</v>
+        <v>395</v>
       </c>
       <c r="G70" t="s">
-        <v>617</v>
+        <v>464</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -4165,22 +3520,22 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="C71" t="s">
-        <v>399</v>
+        <v>319</v>
       </c>
       <c r="D71" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E71" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F71" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G71" t="s">
-        <v>618</v>
+        <v>465</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -4188,22 +3543,22 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>259</v>
+        <v>199</v>
       </c>
       <c r="C72" t="s">
-        <v>421</v>
+        <v>320</v>
       </c>
       <c r="D72" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E72" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F72" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G72" t="s">
-        <v>619</v>
+        <v>466</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -4211,22 +3566,22 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="C73" t="s">
-        <v>422</v>
+        <v>321</v>
       </c>
       <c r="D73" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E73" t="s">
-        <v>536</v>
+        <v>379</v>
       </c>
       <c r="F73" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G73" t="s">
-        <v>620</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -4234,22 +3589,22 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="C74" t="s">
-        <v>423</v>
+        <v>322</v>
       </c>
       <c r="D74" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E74" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F74" t="s">
-        <v>548</v>
+        <v>394</v>
       </c>
       <c r="G74" t="s">
-        <v>621</v>
+        <v>468</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -4257,22 +3612,22 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>262</v>
+        <v>202</v>
       </c>
       <c r="C75" t="s">
-        <v>424</v>
+        <v>323</v>
       </c>
       <c r="D75" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E75" t="s">
-        <v>524</v>
+        <v>381</v>
       </c>
       <c r="F75" t="s">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="G75" t="s">
-        <v>622</v>
+        <v>469</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -4280,22 +3635,22 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>263</v>
+        <v>203</v>
       </c>
       <c r="C76" t="s">
-        <v>425</v>
+        <v>324</v>
       </c>
       <c r="D76" t="s">
-        <v>516</v>
+        <v>376</v>
       </c>
       <c r="E76" t="s">
-        <v>524</v>
+        <v>384</v>
       </c>
       <c r="F76" t="s">
-        <v>547</v>
+        <v>393</v>
       </c>
       <c r="G76" t="s">
-        <v>623</v>
+        <v>470</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -4303,22 +3658,22 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>264</v>
+        <v>204</v>
       </c>
       <c r="C77" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
       <c r="D77" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E77" t="s">
-        <v>524</v>
+        <v>387</v>
       </c>
       <c r="F77" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G77" t="s">
-        <v>624</v>
+        <v>471</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -4326,22 +3681,22 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>265</v>
+        <v>205</v>
       </c>
       <c r="C78" t="s">
-        <v>427</v>
+        <v>326</v>
       </c>
       <c r="D78" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E78" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F78" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G78" t="s">
-        <v>625</v>
+        <v>472</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -4349,22 +3704,22 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="C79" t="s">
-        <v>428</v>
+        <v>327</v>
       </c>
       <c r="D79" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E79" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F79" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G79" t="s">
-        <v>626</v>
+        <v>473</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4372,22 +3727,22 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="C80" t="s">
-        <v>429</v>
+        <v>328</v>
       </c>
       <c r="D80" t="s">
-        <v>516</v>
+        <v>376</v>
       </c>
       <c r="E80" t="s">
-        <v>526</v>
+        <v>385</v>
       </c>
       <c r="F80" t="s">
-        <v>548</v>
+        <v>393</v>
       </c>
       <c r="G80" t="s">
-        <v>627</v>
+        <v>474</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -4395,22 +3750,22 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C81" t="s">
-        <v>373</v>
+        <v>329</v>
       </c>
       <c r="D81" t="s">
-        <v>522</v>
+        <v>375</v>
       </c>
       <c r="E81" t="s">
-        <v>537</v>
+        <v>383</v>
       </c>
       <c r="F81" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G81" t="s">
-        <v>628</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -4418,22 +3773,22 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="C82" t="s">
-        <v>430</v>
+        <v>330</v>
       </c>
       <c r="D82" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E82" t="s">
-        <v>529</v>
+        <v>379</v>
       </c>
       <c r="F82" t="s">
-        <v>546</v>
+        <v>395</v>
       </c>
       <c r="G82" t="s">
-        <v>629</v>
+        <v>476</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -4441,22 +3796,22 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>269</v>
+        <v>210</v>
       </c>
       <c r="C83" t="s">
-        <v>431</v>
+        <v>331</v>
       </c>
       <c r="D83" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E83" t="s">
-        <v>532</v>
+        <v>389</v>
       </c>
       <c r="F83" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G83" t="s">
-        <v>630</v>
+        <v>477</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4464,22 +3819,22 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>270</v>
+        <v>177</v>
       </c>
       <c r="C84" t="s">
-        <v>432</v>
+        <v>298</v>
       </c>
       <c r="D84" t="s">
-        <v>516</v>
+        <v>376</v>
       </c>
       <c r="E84" t="s">
-        <v>524</v>
+        <v>385</v>
       </c>
       <c r="F84" t="s">
-        <v>547</v>
+        <v>393</v>
       </c>
       <c r="G84" t="s">
-        <v>631</v>
+        <v>478</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4487,22 +3842,22 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>271</v>
+        <v>211</v>
       </c>
       <c r="C85" t="s">
-        <v>433</v>
+        <v>332</v>
       </c>
       <c r="D85" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E85" t="s">
-        <v>524</v>
+        <v>387</v>
       </c>
       <c r="F85" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G85" t="s">
-        <v>632</v>
+        <v>479</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4510,22 +3865,22 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>272</v>
+        <v>212</v>
       </c>
       <c r="C86" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="D86" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E86" t="s">
-        <v>530</v>
+        <v>379</v>
       </c>
       <c r="F86" t="s">
-        <v>546</v>
+        <v>394</v>
       </c>
       <c r="G86" t="s">
-        <v>633</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4533,22 +3888,22 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C87" t="s">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D87" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E87" t="s">
-        <v>528</v>
+        <v>379</v>
       </c>
       <c r="F87" t="s">
-        <v>548</v>
+        <v>394</v>
       </c>
       <c r="G87" t="s">
-        <v>634</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4556,22 +3911,22 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="C88" t="s">
-        <v>435</v>
+        <v>335</v>
       </c>
       <c r="D88" t="s">
-        <v>516</v>
+        <v>376</v>
       </c>
       <c r="E88" t="s">
-        <v>524</v>
+        <v>391</v>
       </c>
       <c r="F88" t="s">
-        <v>548</v>
+        <v>393</v>
       </c>
       <c r="G88" t="s">
-        <v>635</v>
+        <v>482</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4579,22 +3934,22 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>274</v>
+        <v>215</v>
       </c>
       <c r="C89" t="s">
-        <v>436</v>
+        <v>336</v>
       </c>
       <c r="D89" t="s">
-        <v>519</v>
+        <v>376</v>
       </c>
       <c r="E89" t="s">
-        <v>528</v>
+        <v>391</v>
       </c>
       <c r="F89" t="s">
-        <v>548</v>
+        <v>393</v>
       </c>
       <c r="G89" t="s">
-        <v>636</v>
+        <v>483</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4602,22 +3957,22 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="C90" t="s">
-        <v>437</v>
+        <v>337</v>
       </c>
       <c r="D90" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E90" t="s">
-        <v>528</v>
+        <v>379</v>
       </c>
       <c r="F90" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G90" t="s">
-        <v>637</v>
+        <v>484</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4625,22 +3980,22 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="C91" t="s">
-        <v>438</v>
+        <v>338</v>
       </c>
       <c r="D91" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E91" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F91" t="s">
-        <v>548</v>
+        <v>394</v>
       </c>
       <c r="G91" t="s">
-        <v>638</v>
+        <v>485</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4648,22 +4003,22 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
       <c r="C92" t="s">
-        <v>439</v>
+        <v>339</v>
       </c>
       <c r="D92" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E92" t="s">
-        <v>534</v>
+        <v>379</v>
       </c>
       <c r="F92" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G92" t="s">
-        <v>639</v>
+        <v>486</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4671,22 +4026,22 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="C93" t="s">
-        <v>401</v>
+        <v>340</v>
       </c>
       <c r="D93" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E93" t="s">
-        <v>530</v>
+        <v>379</v>
       </c>
       <c r="F93" t="s">
-        <v>546</v>
+        <v>394</v>
       </c>
       <c r="G93" t="s">
-        <v>640</v>
+        <v>487</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4694,22 +4049,22 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>278</v>
+        <v>220</v>
       </c>
       <c r="C94" t="s">
-        <v>440</v>
+        <v>341</v>
       </c>
       <c r="D94" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E94" t="s">
-        <v>532</v>
+        <v>379</v>
       </c>
       <c r="F94" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G94" t="s">
-        <v>641</v>
+        <v>488</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4717,22 +4072,22 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C95" t="s">
-        <v>392</v>
+        <v>342</v>
       </c>
       <c r="D95" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E95" t="s">
-        <v>532</v>
+        <v>379</v>
       </c>
       <c r="F95" t="s">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="G95" t="s">
-        <v>642</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4740,22 +4095,22 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="C96" t="s">
-        <v>441</v>
+        <v>343</v>
       </c>
       <c r="D96" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E96" t="s">
-        <v>524</v>
+        <v>387</v>
       </c>
       <c r="F96" t="s">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="G96" t="s">
-        <v>643</v>
+        <v>490</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4763,22 +4118,22 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>280</v>
+        <v>223</v>
       </c>
       <c r="C97" t="s">
-        <v>442</v>
+        <v>344</v>
       </c>
       <c r="D97" t="s">
-        <v>516</v>
+        <v>378</v>
       </c>
       <c r="E97" t="s">
-        <v>524</v>
+        <v>392</v>
       </c>
       <c r="F97" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G97" t="s">
-        <v>644</v>
+        <v>491</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4786,22 +4141,22 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>281</v>
+        <v>224</v>
       </c>
       <c r="C98" t="s">
-        <v>443</v>
+        <v>345</v>
       </c>
       <c r="D98" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E98" t="s">
-        <v>536</v>
+        <v>379</v>
       </c>
       <c r="F98" t="s">
-        <v>546</v>
+        <v>395</v>
       </c>
       <c r="G98" t="s">
-        <v>645</v>
+        <v>492</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4809,22 +4164,22 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>282</v>
+        <v>225</v>
       </c>
       <c r="C99" t="s">
-        <v>444</v>
+        <v>346</v>
       </c>
       <c r="D99" t="s">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="E99" t="s">
-        <v>536</v>
+        <v>379</v>
       </c>
       <c r="F99" t="s">
-        <v>546</v>
+        <v>394</v>
       </c>
       <c r="G99" t="s">
-        <v>646</v>
+        <v>493</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4832,22 +4187,22 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C100" t="s">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="D100" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E100" t="s">
-        <v>528</v>
+        <v>379</v>
       </c>
       <c r="F100" t="s">
-        <v>548</v>
+        <v>394</v>
       </c>
       <c r="G100" t="s">
-        <v>647</v>
+        <v>494</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4855,22 +4210,22 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="C101" t="s">
-        <v>445</v>
+        <v>348</v>
       </c>
       <c r="D101" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E101" t="s">
-        <v>524</v>
+        <v>387</v>
       </c>
       <c r="F101" t="s">
-        <v>548</v>
+        <v>395</v>
       </c>
       <c r="G101" t="s">
-        <v>648</v>
+        <v>495</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4878,22 +4233,22 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="C102" t="s">
-        <v>406</v>
+        <v>349</v>
       </c>
       <c r="D102" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E102" t="s">
-        <v>532</v>
+        <v>379</v>
       </c>
       <c r="F102" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G102" t="s">
-        <v>649</v>
+        <v>496</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4901,22 +4256,22 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>284</v>
+        <v>229</v>
       </c>
       <c r="C103" t="s">
-        <v>446</v>
+        <v>350</v>
       </c>
       <c r="D103" t="s">
-        <v>516</v>
+        <v>373</v>
       </c>
       <c r="E103" t="s">
-        <v>524</v>
+        <v>380</v>
       </c>
       <c r="F103" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G103" t="s">
-        <v>650</v>
+        <v>497</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4924,22 +4279,22 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>285</v>
+        <v>230</v>
       </c>
       <c r="C104" t="s">
-        <v>447</v>
+        <v>351</v>
       </c>
       <c r="D104" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E104" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F104" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G104" t="s">
-        <v>651</v>
+        <v>498</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4947,22 +4302,22 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C105" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="D105" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E105" t="s">
-        <v>528</v>
+        <v>387</v>
       </c>
       <c r="F105" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G105" t="s">
-        <v>652</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4970,22 +4325,22 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="C106" t="s">
-        <v>448</v>
+        <v>353</v>
       </c>
       <c r="D106" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E106" t="s">
-        <v>524</v>
+        <v>387</v>
       </c>
       <c r="F106" t="s">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="G106" t="s">
-        <v>653</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4993,22 +4348,22 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="C107" t="s">
-        <v>449</v>
+        <v>354</v>
       </c>
       <c r="D107" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E107" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F107" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G107" t="s">
-        <v>654</v>
+        <v>501</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -5016,22 +4371,22 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="C108" t="s">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="D108" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E108" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F108" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G108" t="s">
-        <v>655</v>
+        <v>502</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -5039,22 +4394,22 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="C109" t="s">
-        <v>451</v>
+        <v>356</v>
       </c>
       <c r="D109" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E109" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F109" t="s">
-        <v>548</v>
+        <v>394</v>
       </c>
       <c r="G109" t="s">
-        <v>656</v>
+        <v>503</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -5062,22 +4417,22 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="C110" t="s">
-        <v>452</v>
+        <v>357</v>
       </c>
       <c r="D110" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E110" t="s">
-        <v>532</v>
+        <v>379</v>
       </c>
       <c r="F110" t="s">
-        <v>548</v>
+        <v>394</v>
       </c>
       <c r="G110" t="s">
-        <v>657</v>
+        <v>504</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -5085,22 +4440,22 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="C111" t="s">
-        <v>453</v>
+        <v>358</v>
       </c>
       <c r="D111" t="s">
-        <v>523</v>
+        <v>372</v>
       </c>
       <c r="E111" t="s">
-        <v>538</v>
+        <v>390</v>
       </c>
       <c r="F111" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G111" t="s">
-        <v>658</v>
+        <v>505</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -5108,22 +4463,22 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="C112" t="s">
-        <v>454</v>
+        <v>359</v>
       </c>
       <c r="D112" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E112" t="s">
-        <v>524</v>
+        <v>387</v>
       </c>
       <c r="F112" t="s">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="G112" t="s">
-        <v>659</v>
+        <v>506</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -5131,22 +4486,22 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="C113" t="s">
-        <v>436</v>
+        <v>360</v>
       </c>
       <c r="D113" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E113" t="s">
-        <v>539</v>
+        <v>379</v>
       </c>
       <c r="F113" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G113" t="s">
-        <v>660</v>
+        <v>507</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -5154,22 +4509,22 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>293</v>
+        <v>240</v>
       </c>
       <c r="C114" t="s">
-        <v>455</v>
+        <v>361</v>
       </c>
       <c r="D114" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E114" t="s">
-        <v>524</v>
+        <v>387</v>
       </c>
       <c r="F114" t="s">
-        <v>548</v>
+        <v>394</v>
       </c>
       <c r="G114" t="s">
-        <v>661</v>
+        <v>508</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -5177,22 +4532,22 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="C115" t="s">
-        <v>456</v>
+        <v>362</v>
       </c>
       <c r="D115" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E115" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F115" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G115" t="s">
-        <v>662</v>
+        <v>509</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -5200,22 +4555,22 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="C116" t="s">
-        <v>457</v>
+        <v>363</v>
       </c>
       <c r="D116" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E116" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F116" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G116" t="s">
-        <v>663</v>
+        <v>510</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -5223,22 +4578,22 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>296</v>
+        <v>243</v>
       </c>
       <c r="C117" t="s">
-        <v>458</v>
+        <v>364</v>
       </c>
       <c r="D117" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E117" t="s">
-        <v>532</v>
+        <v>379</v>
       </c>
       <c r="F117" t="s">
-        <v>548</v>
+        <v>394</v>
       </c>
       <c r="G117" t="s">
-        <v>664</v>
+        <v>511</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -5246,22 +4601,22 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>297</v>
+        <v>244</v>
       </c>
       <c r="C118" t="s">
-        <v>459</v>
+        <v>365</v>
       </c>
       <c r="D118" t="s">
-        <v>519</v>
+        <v>372</v>
       </c>
       <c r="E118" t="s">
-        <v>532</v>
+        <v>379</v>
       </c>
       <c r="F118" t="s">
-        <v>546</v>
+        <v>394</v>
       </c>
       <c r="G118" t="s">
-        <v>665</v>
+        <v>512</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -5269,22 +4624,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="C119" t="s">
-        <v>460</v>
+        <v>366</v>
       </c>
       <c r="D119" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E119" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F119" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G119" t="s">
-        <v>666</v>
+        <v>513</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -5292,22 +4647,22 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>299</v>
+        <v>246</v>
       </c>
       <c r="C120" t="s">
-        <v>461</v>
+        <v>367</v>
       </c>
       <c r="D120" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E120" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F120" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G120" t="s">
-        <v>667</v>
+        <v>514</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -5315,22 +4670,22 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>300</v>
+        <v>247</v>
       </c>
       <c r="C121" t="s">
-        <v>462</v>
+        <v>368</v>
       </c>
       <c r="D121" t="s">
-        <v>517</v>
+        <v>372</v>
       </c>
       <c r="E121" t="s">
-        <v>525</v>
+        <v>379</v>
       </c>
       <c r="F121" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G121" t="s">
-        <v>668</v>
+        <v>515</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -5338,22 +4693,22 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C122" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="D122" t="s">
+        <v>372</v>
+      </c>
+      <c r="E122" t="s">
+        <v>379</v>
+      </c>
+      <c r="F122" t="s">
+        <v>394</v>
+      </c>
+      <c r="G122" t="s">
         <v>516</v>
-      </c>
-      <c r="E122" t="s">
-        <v>524</v>
-      </c>
-      <c r="F122" t="s">
-        <v>548</v>
-      </c>
-      <c r="G122" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -5361,22 +4716,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>301</v>
+        <v>249</v>
       </c>
       <c r="C123" t="s">
-        <v>463</v>
+        <v>370</v>
       </c>
       <c r="D123" t="s">
-        <v>516</v>
+        <v>372</v>
       </c>
       <c r="E123" t="s">
-        <v>524</v>
+        <v>379</v>
       </c>
       <c r="F123" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G123" t="s">
-        <v>670</v>
+        <v>517</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -5384,1448 +4739,22 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="C124" t="s">
-        <v>464</v>
+        <v>371</v>
       </c>
       <c r="D124" t="s">
-        <v>516</v>
+        <v>375</v>
       </c>
       <c r="E124" t="s">
-        <v>539</v>
+        <v>387</v>
       </c>
       <c r="F124" t="s">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="G124" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
-      <c r="A125" t="s">
-        <v>130</v>
-      </c>
-      <c r="B125" t="s">
-        <v>303</v>
-      </c>
-      <c r="C125" t="s">
-        <v>465</v>
-      </c>
-      <c r="D125" t="s">
-        <v>519</v>
-      </c>
-      <c r="E125" t="s">
-        <v>540</v>
-      </c>
-      <c r="F125" t="s">
-        <v>547</v>
-      </c>
-      <c r="G125" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
-      <c r="A126" t="s">
-        <v>131</v>
-      </c>
-      <c r="B126" t="s">
-        <v>304</v>
-      </c>
-      <c r="C126" t="s">
-        <v>466</v>
-      </c>
-      <c r="D126" t="s">
-        <v>519</v>
-      </c>
-      <c r="E126" t="s">
-        <v>532</v>
-      </c>
-      <c r="F126" t="s">
-        <v>547</v>
-      </c>
-      <c r="G126" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="A127" t="s">
-        <v>132</v>
-      </c>
-      <c r="B127" t="s">
-        <v>305</v>
-      </c>
-      <c r="C127" t="s">
-        <v>467</v>
-      </c>
-      <c r="D127" t="s">
-        <v>516</v>
-      </c>
-      <c r="E127" t="s">
-        <v>524</v>
-      </c>
-      <c r="F127" t="s">
-        <v>547</v>
-      </c>
-      <c r="G127" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
-      <c r="A128" t="s">
-        <v>133</v>
-      </c>
-      <c r="B128" t="s">
-        <v>288</v>
-      </c>
-      <c r="C128" t="s">
-        <v>450</v>
-      </c>
-      <c r="D128" t="s">
-        <v>516</v>
-      </c>
-      <c r="E128" t="s">
-        <v>534</v>
-      </c>
-      <c r="F128" t="s">
-        <v>547</v>
-      </c>
-      <c r="G128" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129" t="s">
-        <v>134</v>
-      </c>
-      <c r="B129" t="s">
-        <v>306</v>
-      </c>
-      <c r="C129" t="s">
-        <v>468</v>
-      </c>
-      <c r="D129" t="s">
-        <v>519</v>
-      </c>
-      <c r="E129" t="s">
-        <v>528</v>
-      </c>
-      <c r="F129" t="s">
-        <v>548</v>
-      </c>
-      <c r="G129" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" t="s">
-        <v>135</v>
-      </c>
-      <c r="B130" t="s">
-        <v>307</v>
-      </c>
-      <c r="C130" t="s">
-        <v>469</v>
-      </c>
-      <c r="D130" t="s">
-        <v>519</v>
-      </c>
-      <c r="E130" t="s">
-        <v>532</v>
-      </c>
-      <c r="F130" t="s">
-        <v>547</v>
-      </c>
-      <c r="G130" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" t="s">
-        <v>136</v>
-      </c>
-      <c r="B131" t="s">
-        <v>308</v>
-      </c>
-      <c r="C131" t="s">
-        <v>470</v>
-      </c>
-      <c r="D131" t="s">
-        <v>523</v>
-      </c>
-      <c r="E131" t="s">
-        <v>541</v>
-      </c>
-      <c r="F131" t="s">
-        <v>548</v>
-      </c>
-      <c r="G131" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" t="s">
-        <v>137</v>
-      </c>
-      <c r="B132" t="s">
-        <v>309</v>
-      </c>
-      <c r="C132" t="s">
-        <v>471</v>
-      </c>
-      <c r="D132" t="s">
-        <v>519</v>
-      </c>
-      <c r="E132" t="s">
-        <v>532</v>
-      </c>
-      <c r="F132" t="s">
-        <v>548</v>
-      </c>
-      <c r="G132" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" t="s">
-        <v>138</v>
-      </c>
-      <c r="B133" t="s">
-        <v>205</v>
-      </c>
-      <c r="C133" t="s">
-        <v>367</v>
-      </c>
-      <c r="D133" t="s">
-        <v>519</v>
-      </c>
-      <c r="E133" t="s">
-        <v>528</v>
-      </c>
-      <c r="F133" t="s">
-        <v>548</v>
-      </c>
-      <c r="G133" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" t="s">
-        <v>139</v>
-      </c>
-      <c r="B134" t="s">
-        <v>310</v>
-      </c>
-      <c r="C134" t="s">
-        <v>472</v>
-      </c>
-      <c r="D134" t="s">
-        <v>516</v>
-      </c>
-      <c r="E134" t="s">
-        <v>524</v>
-      </c>
-      <c r="F134" t="s">
-        <v>547</v>
-      </c>
-      <c r="G134" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135" t="s">
-        <v>140</v>
-      </c>
-      <c r="B135" t="s">
-        <v>311</v>
-      </c>
-      <c r="C135" t="s">
-        <v>473</v>
-      </c>
-      <c r="D135" t="s">
-        <v>516</v>
-      </c>
-      <c r="E135" t="s">
-        <v>524</v>
-      </c>
-      <c r="F135" t="s">
-        <v>547</v>
-      </c>
-      <c r="G135" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="A136" t="s">
-        <v>141</v>
-      </c>
-      <c r="B136" t="s">
-        <v>312</v>
-      </c>
-      <c r="C136" t="s">
-        <v>474</v>
-      </c>
-      <c r="D136" t="s">
-        <v>516</v>
-      </c>
-      <c r="E136" t="s">
-        <v>524</v>
-      </c>
-      <c r="F136" t="s">
-        <v>547</v>
-      </c>
-      <c r="G136" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137" t="s">
-        <v>142</v>
-      </c>
-      <c r="B137" t="s">
-        <v>313</v>
-      </c>
-      <c r="C137" t="s">
-        <v>475</v>
-      </c>
-      <c r="D137" t="s">
-        <v>516</v>
-      </c>
-      <c r="E137" t="s">
-        <v>524</v>
-      </c>
-      <c r="F137" t="s">
-        <v>547</v>
-      </c>
-      <c r="G137" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="A138" t="s">
-        <v>143</v>
-      </c>
-      <c r="B138" t="s">
-        <v>314</v>
-      </c>
-      <c r="C138" t="s">
-        <v>476</v>
-      </c>
-      <c r="D138" t="s">
-        <v>516</v>
-      </c>
-      <c r="E138" t="s">
-        <v>524</v>
-      </c>
-      <c r="F138" t="s">
-        <v>547</v>
-      </c>
-      <c r="G138" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" t="s">
-        <v>144</v>
-      </c>
-      <c r="B139" t="s">
-        <v>315</v>
-      </c>
-      <c r="C139" t="s">
-        <v>477</v>
-      </c>
-      <c r="D139" t="s">
-        <v>516</v>
-      </c>
-      <c r="E139" t="s">
-        <v>524</v>
-      </c>
-      <c r="F139" t="s">
-        <v>546</v>
-      </c>
-      <c r="G139" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140" t="s">
-        <v>145</v>
-      </c>
-      <c r="B140" t="s">
-        <v>316</v>
-      </c>
-      <c r="C140" t="s">
-        <v>478</v>
-      </c>
-      <c r="D140" t="s">
-        <v>519</v>
-      </c>
-      <c r="E140" t="s">
-        <v>542</v>
-      </c>
-      <c r="F140" t="s">
-        <v>547</v>
-      </c>
-      <c r="G140" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141" t="s">
-        <v>146</v>
-      </c>
-      <c r="B141" t="s">
-        <v>317</v>
-      </c>
-      <c r="C141" t="s">
-        <v>479</v>
-      </c>
-      <c r="D141" t="s">
-        <v>516</v>
-      </c>
-      <c r="E141" t="s">
-        <v>524</v>
-      </c>
-      <c r="F141" t="s">
-        <v>546</v>
-      </c>
-      <c r="G141" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="A142" t="s">
-        <v>147</v>
-      </c>
-      <c r="B142" t="s">
-        <v>318</v>
-      </c>
-      <c r="C142" t="s">
-        <v>480</v>
-      </c>
-      <c r="D142" t="s">
-        <v>516</v>
-      </c>
-      <c r="E142" t="s">
-        <v>535</v>
-      </c>
-      <c r="F142" t="s">
-        <v>547</v>
-      </c>
-      <c r="G142" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="A143" t="s">
-        <v>148</v>
-      </c>
-      <c r="B143" t="s">
-        <v>319</v>
-      </c>
-      <c r="C143" t="s">
-        <v>481</v>
-      </c>
-      <c r="D143" t="s">
-        <v>519</v>
-      </c>
-      <c r="E143" t="s">
-        <v>532</v>
-      </c>
-      <c r="F143" t="s">
-        <v>548</v>
-      </c>
-      <c r="G143" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
-      <c r="A144" t="s">
-        <v>149</v>
-      </c>
-      <c r="B144" t="s">
-        <v>279</v>
-      </c>
-      <c r="C144" t="s">
-        <v>441</v>
-      </c>
-      <c r="D144" t="s">
-        <v>516</v>
-      </c>
-      <c r="E144" t="s">
-        <v>524</v>
-      </c>
-      <c r="F144" t="s">
-        <v>547</v>
-      </c>
-      <c r="G144" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145" t="s">
-        <v>150</v>
-      </c>
-      <c r="B145" t="s">
-        <v>320</v>
-      </c>
-      <c r="C145" t="s">
-        <v>482</v>
-      </c>
-      <c r="D145" t="s">
-        <v>516</v>
-      </c>
-      <c r="E145" t="s">
-        <v>534</v>
-      </c>
-      <c r="F145" t="s">
-        <v>547</v>
-      </c>
-      <c r="G145" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
-      <c r="A146" t="s">
-        <v>151</v>
-      </c>
-      <c r="B146" t="s">
-        <v>321</v>
-      </c>
-      <c r="C146" t="s">
-        <v>483</v>
-      </c>
-      <c r="D146" t="s">
-        <v>516</v>
-      </c>
-      <c r="E146" t="s">
-        <v>526</v>
-      </c>
-      <c r="F146" t="s">
-        <v>547</v>
-      </c>
-      <c r="G146" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="A147" t="s">
-        <v>152</v>
-      </c>
-      <c r="B147" t="s">
-        <v>253</v>
-      </c>
-      <c r="C147" t="s">
-        <v>415</v>
-      </c>
-      <c r="D147" t="s">
-        <v>516</v>
-      </c>
-      <c r="E147" t="s">
-        <v>524</v>
-      </c>
-      <c r="F147" t="s">
-        <v>547</v>
-      </c>
-      <c r="G147" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="A148" t="s">
-        <v>153</v>
-      </c>
-      <c r="B148" t="s">
-        <v>322</v>
-      </c>
-      <c r="C148" t="s">
-        <v>484</v>
-      </c>
-      <c r="D148" t="s">
-        <v>519</v>
-      </c>
-      <c r="E148" t="s">
-        <v>543</v>
-      </c>
-      <c r="F148" t="s">
-        <v>547</v>
-      </c>
-      <c r="G148" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149" t="s">
-        <v>154</v>
-      </c>
-      <c r="B149" t="s">
-        <v>323</v>
-      </c>
-      <c r="C149" t="s">
-        <v>485</v>
-      </c>
-      <c r="D149" t="s">
-        <v>516</v>
-      </c>
-      <c r="E149" t="s">
-        <v>524</v>
-      </c>
-      <c r="F149" t="s">
-        <v>547</v>
-      </c>
-      <c r="G149" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150" t="s">
-        <v>155</v>
-      </c>
-      <c r="B150" t="s">
-        <v>324</v>
-      </c>
-      <c r="C150" t="s">
-        <v>486</v>
-      </c>
-      <c r="D150" t="s">
-        <v>516</v>
-      </c>
-      <c r="E150" t="s">
-        <v>534</v>
-      </c>
-      <c r="F150" t="s">
-        <v>547</v>
-      </c>
-      <c r="G150" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="A151" t="s">
-        <v>156</v>
-      </c>
-      <c r="B151" t="s">
-        <v>325</v>
-      </c>
-      <c r="C151" t="s">
-        <v>487</v>
-      </c>
-      <c r="D151" t="s">
-        <v>516</v>
-      </c>
-      <c r="E151" t="s">
-        <v>524</v>
-      </c>
-      <c r="F151" t="s">
-        <v>546</v>
-      </c>
-      <c r="G151" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" t="s">
-        <v>157</v>
-      </c>
-      <c r="B152" t="s">
-        <v>326</v>
-      </c>
-      <c r="C152" t="s">
-        <v>488</v>
-      </c>
-      <c r="D152" t="s">
-        <v>516</v>
-      </c>
-      <c r="E152" t="s">
-        <v>524</v>
-      </c>
-      <c r="F152" t="s">
-        <v>546</v>
-      </c>
-      <c r="G152" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153" t="s">
-        <v>158</v>
-      </c>
-      <c r="B153" t="s">
-        <v>327</v>
-      </c>
-      <c r="C153" t="s">
-        <v>489</v>
-      </c>
-      <c r="D153" t="s">
-        <v>519</v>
-      </c>
-      <c r="E153" t="s">
-        <v>532</v>
-      </c>
-      <c r="F153" t="s">
-        <v>546</v>
-      </c>
-      <c r="G153" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154" t="s">
-        <v>159</v>
-      </c>
-      <c r="B154" t="s">
-        <v>209</v>
-      </c>
-      <c r="C154" t="s">
-        <v>371</v>
-      </c>
-      <c r="D154" t="s">
-        <v>516</v>
-      </c>
-      <c r="E154" t="s">
-        <v>524</v>
-      </c>
-      <c r="F154" t="s">
-        <v>547</v>
-      </c>
-      <c r="G154" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="A155" t="s">
-        <v>160</v>
-      </c>
-      <c r="B155" t="s">
-        <v>304</v>
-      </c>
-      <c r="C155" t="s">
-        <v>466</v>
-      </c>
-      <c r="D155" t="s">
-        <v>516</v>
-      </c>
-      <c r="E155" t="s">
-        <v>524</v>
-      </c>
-      <c r="F155" t="s">
-        <v>547</v>
-      </c>
-      <c r="G155" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156" t="s">
-        <v>161</v>
-      </c>
-      <c r="B156" t="s">
-        <v>328</v>
-      </c>
-      <c r="C156" t="s">
-        <v>490</v>
-      </c>
-      <c r="D156" t="s">
-        <v>519</v>
-      </c>
-      <c r="E156" t="s">
-        <v>532</v>
-      </c>
-      <c r="F156" t="s">
-        <v>547</v>
-      </c>
-      <c r="G156" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" t="s">
-        <v>162</v>
-      </c>
-      <c r="B157" t="s">
-        <v>329</v>
-      </c>
-      <c r="C157" t="s">
-        <v>491</v>
-      </c>
-      <c r="D157" t="s">
-        <v>519</v>
-      </c>
-      <c r="E157" t="s">
-        <v>532</v>
-      </c>
-      <c r="F157" t="s">
-        <v>547</v>
-      </c>
-      <c r="G157" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="A158" t="s">
-        <v>163</v>
-      </c>
-      <c r="B158" t="s">
-        <v>330</v>
-      </c>
-      <c r="C158" t="s">
-        <v>492</v>
-      </c>
-      <c r="D158" t="s">
-        <v>516</v>
-      </c>
-      <c r="E158" t="s">
-        <v>524</v>
-      </c>
-      <c r="F158" t="s">
-        <v>547</v>
-      </c>
-      <c r="G158" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159" t="s">
-        <v>164</v>
-      </c>
-      <c r="B159" t="s">
-        <v>331</v>
-      </c>
-      <c r="C159" t="s">
-        <v>493</v>
-      </c>
-      <c r="D159" t="s">
-        <v>516</v>
-      </c>
-      <c r="E159" t="s">
-        <v>524</v>
-      </c>
-      <c r="F159" t="s">
-        <v>547</v>
-      </c>
-      <c r="G159" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
-      <c r="A160" t="s">
-        <v>165</v>
-      </c>
-      <c r="B160" t="s">
-        <v>332</v>
-      </c>
-      <c r="C160" t="s">
-        <v>494</v>
-      </c>
-      <c r="D160" t="s">
-        <v>516</v>
-      </c>
-      <c r="E160" t="s">
-        <v>524</v>
-      </c>
-      <c r="F160" t="s">
-        <v>547</v>
-      </c>
-      <c r="G160" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161" t="s">
-        <v>166</v>
-      </c>
-      <c r="B161" t="s">
-        <v>333</v>
-      </c>
-      <c r="C161" t="s">
-        <v>495</v>
-      </c>
-      <c r="D161" t="s">
-        <v>516</v>
-      </c>
-      <c r="E161" t="s">
-        <v>524</v>
-      </c>
-      <c r="F161" t="s">
-        <v>547</v>
-      </c>
-      <c r="G161" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162" t="s">
-        <v>167</v>
-      </c>
-      <c r="B162" t="s">
-        <v>334</v>
-      </c>
-      <c r="C162" t="s">
-        <v>496</v>
-      </c>
-      <c r="D162" t="s">
-        <v>519</v>
-      </c>
-      <c r="E162" t="s">
-        <v>532</v>
-      </c>
-      <c r="F162" t="s">
-        <v>547</v>
-      </c>
-      <c r="G162" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
-      <c r="A163" t="s">
-        <v>168</v>
-      </c>
-      <c r="B163" t="s">
-        <v>335</v>
-      </c>
-      <c r="C163" t="s">
-        <v>497</v>
-      </c>
-      <c r="D163" t="s">
-        <v>516</v>
-      </c>
-      <c r="E163" t="s">
-        <v>524</v>
-      </c>
-      <c r="F163" t="s">
-        <v>547</v>
-      </c>
-      <c r="G163" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
-      <c r="A164" t="s">
-        <v>169</v>
-      </c>
-      <c r="B164" t="s">
-        <v>336</v>
-      </c>
-      <c r="C164" t="s">
-        <v>498</v>
-      </c>
-      <c r="D164" t="s">
-        <v>516</v>
-      </c>
-      <c r="E164" t="s">
-        <v>524</v>
-      </c>
-      <c r="F164" t="s">
-        <v>547</v>
-      </c>
-      <c r="G164" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
-      <c r="A165" t="s">
-        <v>170</v>
-      </c>
-      <c r="B165" t="s">
-        <v>337</v>
-      </c>
-      <c r="C165" t="s">
-        <v>499</v>
-      </c>
-      <c r="D165" t="s">
-        <v>516</v>
-      </c>
-      <c r="E165" t="s">
-        <v>524</v>
-      </c>
-      <c r="F165" t="s">
-        <v>547</v>
-      </c>
-      <c r="G165" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
-      <c r="A166" t="s">
-        <v>171</v>
-      </c>
-      <c r="B166" t="s">
-        <v>338</v>
-      </c>
-      <c r="C166" t="s">
-        <v>500</v>
-      </c>
-      <c r="D166" t="s">
-        <v>516</v>
-      </c>
-      <c r="E166" t="s">
-        <v>524</v>
-      </c>
-      <c r="F166" t="s">
-        <v>547</v>
-      </c>
-      <c r="G166" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" t="s">
-        <v>172</v>
-      </c>
-      <c r="B167" t="s">
-        <v>248</v>
-      </c>
-      <c r="C167" t="s">
-        <v>410</v>
-      </c>
-      <c r="D167" t="s">
-        <v>519</v>
-      </c>
-      <c r="E167" t="s">
-        <v>532</v>
-      </c>
-      <c r="F167" t="s">
-        <v>547</v>
-      </c>
-      <c r="G167" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" t="s">
-        <v>173</v>
-      </c>
-      <c r="B168" t="s">
-        <v>339</v>
-      </c>
-      <c r="C168" t="s">
-        <v>501</v>
-      </c>
-      <c r="D168" t="s">
-        <v>516</v>
-      </c>
-      <c r="E168" t="s">
-        <v>524</v>
-      </c>
-      <c r="F168" t="s">
-        <v>547</v>
-      </c>
-      <c r="G168" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" t="s">
-        <v>174</v>
-      </c>
-      <c r="B169" t="s">
-        <v>340</v>
-      </c>
-      <c r="C169" t="s">
-        <v>502</v>
-      </c>
-      <c r="D169" t="s">
-        <v>516</v>
-      </c>
-      <c r="E169" t="s">
-        <v>524</v>
-      </c>
-      <c r="F169" t="s">
-        <v>547</v>
-      </c>
-      <c r="G169" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170" t="s">
-        <v>175</v>
-      </c>
-      <c r="B170" t="s">
-        <v>304</v>
-      </c>
-      <c r="C170" t="s">
-        <v>466</v>
-      </c>
-      <c r="D170" t="s">
-        <v>516</v>
-      </c>
-      <c r="E170" t="s">
-        <v>524</v>
-      </c>
-      <c r="F170" t="s">
-        <v>547</v>
-      </c>
-      <c r="G170" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171" t="s">
-        <v>176</v>
-      </c>
-      <c r="B171" t="s">
-        <v>341</v>
-      </c>
-      <c r="C171" t="s">
-        <v>503</v>
-      </c>
-      <c r="D171" t="s">
-        <v>516</v>
-      </c>
-      <c r="E171" t="s">
-        <v>524</v>
-      </c>
-      <c r="F171" t="s">
-        <v>547</v>
-      </c>
-      <c r="G171" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172" t="s">
-        <v>177</v>
-      </c>
-      <c r="B172" t="s">
-        <v>296</v>
-      </c>
-      <c r="C172" t="s">
-        <v>458</v>
-      </c>
-      <c r="D172" t="s">
-        <v>519</v>
-      </c>
-      <c r="E172" t="s">
-        <v>528</v>
-      </c>
-      <c r="F172" t="s">
-        <v>546</v>
-      </c>
-      <c r="G172" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="A173" t="s">
-        <v>178</v>
-      </c>
-      <c r="B173" t="s">
-        <v>342</v>
-      </c>
-      <c r="C173" t="s">
-        <v>504</v>
-      </c>
-      <c r="D173" t="s">
-        <v>516</v>
-      </c>
-      <c r="E173" t="s">
-        <v>524</v>
-      </c>
-      <c r="F173" t="s">
-        <v>547</v>
-      </c>
-      <c r="G173" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
-      <c r="A174" t="s">
-        <v>179</v>
-      </c>
-      <c r="B174" t="s">
-        <v>343</v>
-      </c>
-      <c r="C174" t="s">
-        <v>505</v>
-      </c>
-      <c r="D174" t="s">
-        <v>519</v>
-      </c>
-      <c r="E174" t="s">
-        <v>528</v>
-      </c>
-      <c r="F174" t="s">
-        <v>546</v>
-      </c>
-      <c r="G174" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
-      <c r="A175" t="s">
-        <v>180</v>
-      </c>
-      <c r="B175" t="s">
-        <v>344</v>
-      </c>
-      <c r="C175" t="s">
-        <v>506</v>
-      </c>
-      <c r="D175" t="s">
-        <v>519</v>
-      </c>
-      <c r="E175" t="s">
-        <v>540</v>
-      </c>
-      <c r="F175" t="s">
-        <v>547</v>
-      </c>
-      <c r="G175" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
-      <c r="A176" t="s">
-        <v>181</v>
-      </c>
-      <c r="B176" t="s">
-        <v>345</v>
-      </c>
-      <c r="C176" t="s">
-        <v>507</v>
-      </c>
-      <c r="D176" t="s">
-        <v>516</v>
-      </c>
-      <c r="E176" t="s">
-        <v>524</v>
-      </c>
-      <c r="F176" t="s">
-        <v>547</v>
-      </c>
-      <c r="G176" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7">
-      <c r="A177" t="s">
-        <v>182</v>
-      </c>
-      <c r="B177" t="s">
-        <v>346</v>
-      </c>
-      <c r="C177" t="s">
-        <v>508</v>
-      </c>
-      <c r="D177" t="s">
-        <v>517</v>
-      </c>
-      <c r="E177" t="s">
-        <v>525</v>
-      </c>
-      <c r="F177" t="s">
-        <v>547</v>
-      </c>
-      <c r="G177" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7">
-      <c r="A178" t="s">
-        <v>183</v>
-      </c>
-      <c r="B178" t="s">
-        <v>240</v>
-      </c>
-      <c r="C178" t="s">
-        <v>402</v>
-      </c>
-      <c r="D178" t="s">
-        <v>523</v>
-      </c>
-      <c r="E178" t="s">
-        <v>544</v>
-      </c>
-      <c r="F178" t="s">
-        <v>547</v>
-      </c>
-      <c r="G178" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
-      <c r="A179" t="s">
-        <v>184</v>
-      </c>
-      <c r="B179" t="s">
-        <v>347</v>
-      </c>
-      <c r="C179" t="s">
-        <v>509</v>
-      </c>
-      <c r="D179" t="s">
-        <v>516</v>
-      </c>
-      <c r="E179" t="s">
-        <v>524</v>
-      </c>
-      <c r="F179" t="s">
-        <v>547</v>
-      </c>
-      <c r="G179" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
-      <c r="A180" t="s">
-        <v>185</v>
-      </c>
-      <c r="B180" t="s">
-        <v>346</v>
-      </c>
-      <c r="C180" t="s">
-        <v>508</v>
-      </c>
-      <c r="D180" t="s">
-        <v>519</v>
-      </c>
-      <c r="E180" t="s">
-        <v>532</v>
-      </c>
-      <c r="F180" t="s">
-        <v>547</v>
-      </c>
-      <c r="G180" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7">
-      <c r="A181" t="s">
-        <v>186</v>
-      </c>
-      <c r="B181" t="s">
-        <v>348</v>
-      </c>
-      <c r="C181" t="s">
-        <v>510</v>
-      </c>
-      <c r="D181" t="s">
-        <v>516</v>
-      </c>
-      <c r="E181" t="s">
-        <v>524</v>
-      </c>
-      <c r="F181" t="s">
-        <v>547</v>
-      </c>
-      <c r="G181" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7">
-      <c r="A182" t="s">
-        <v>187</v>
-      </c>
-      <c r="B182" t="s">
-        <v>349</v>
-      </c>
-      <c r="C182" t="s">
-        <v>511</v>
-      </c>
-      <c r="D182" t="s">
-        <v>523</v>
-      </c>
-      <c r="E182" t="s">
-        <v>545</v>
-      </c>
-      <c r="F182" t="s">
-        <v>547</v>
-      </c>
-      <c r="G182" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
-      <c r="A183" t="s">
-        <v>188</v>
-      </c>
-      <c r="B183" t="s">
-        <v>350</v>
-      </c>
-      <c r="C183" t="s">
-        <v>512</v>
-      </c>
-      <c r="D183" t="s">
-        <v>519</v>
-      </c>
-      <c r="E183" t="s">
-        <v>532</v>
-      </c>
-      <c r="F183" t="s">
-        <v>547</v>
-      </c>
-      <c r="G183" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7">
-      <c r="A184" t="s">
-        <v>189</v>
-      </c>
-      <c r="B184" t="s">
-        <v>351</v>
-      </c>
-      <c r="C184" t="s">
-        <v>513</v>
-      </c>
-      <c r="D184" t="s">
-        <v>516</v>
-      </c>
-      <c r="E184" t="s">
-        <v>526</v>
-      </c>
-      <c r="F184" t="s">
-        <v>546</v>
-      </c>
-      <c r="G184" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7">
-      <c r="A185" t="s">
-        <v>190</v>
-      </c>
-      <c r="B185" t="s">
-        <v>352</v>
-      </c>
-      <c r="C185" t="s">
-        <v>514</v>
-      </c>
-      <c r="D185" t="s">
-        <v>516</v>
-      </c>
-      <c r="E185" t="s">
-        <v>524</v>
-      </c>
-      <c r="F185" t="s">
-        <v>547</v>
-      </c>
-      <c r="G185" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7">
-      <c r="A186" t="s">
-        <v>191</v>
-      </c>
-      <c r="B186" t="s">
-        <v>353</v>
-      </c>
-      <c r="C186" t="s">
-        <v>515</v>
-      </c>
-      <c r="D186" t="s">
-        <v>516</v>
-      </c>
-      <c r="E186" t="s">
-        <v>524</v>
-      </c>
-      <c r="F186" t="s">
-        <v>546</v>
-      </c>
-      <c r="G186" t="s">
-        <v>733</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
